--- a/artfynd/A 43083-2026 artfynd.xlsx
+++ b/artfynd/A 43083-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153468</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153469</v>
       </c>
       <c r="B3" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153493</v>
       </c>
       <c r="B4" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153495</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137153496</v>
       </c>
       <c r="B6" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>137153497</v>
       </c>
       <c r="B7" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2026 artfynd.xlsx
+++ b/artfynd/A 43083-2026 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>137153493</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153495</v>
       </c>
       <c r="B5" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137153496</v>
       </c>
       <c r="B6" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>137153497</v>
       </c>
       <c r="B7" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2026 artfynd.xlsx
+++ b/artfynd/A 43083-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153468</v>
       </c>
       <c r="B2" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153469</v>
       </c>
       <c r="B3" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153493</v>
       </c>
       <c r="B4" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153495</v>
       </c>
       <c r="B5" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137153496</v>
       </c>
       <c r="B6" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>137153497</v>
       </c>
       <c r="B7" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2026 artfynd.xlsx
+++ b/artfynd/A 43083-2026 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>137153493</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153495</v>
       </c>
       <c r="B5" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137153496</v>
       </c>
       <c r="B6" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>137153497</v>
       </c>
       <c r="B7" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2026 artfynd.xlsx
+++ b/artfynd/A 43083-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153468</v>
       </c>
       <c r="B2" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153469</v>
       </c>
       <c r="B3" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153493</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153495</v>
       </c>
       <c r="B5" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137153496</v>
       </c>
       <c r="B6" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>137153497</v>
       </c>
       <c r="B7" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2026 artfynd.xlsx
+++ b/artfynd/A 43083-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153468</v>
       </c>
       <c r="B2" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153469</v>
       </c>
       <c r="B3" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153493</v>
       </c>
       <c r="B4" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153495</v>
       </c>
       <c r="B5" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137153496</v>
       </c>
       <c r="B6" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>137153497</v>
       </c>
       <c r="B7" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2026 artfynd.xlsx
+++ b/artfynd/A 43083-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153468</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153469</v>
       </c>
       <c r="B3" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153493</v>
       </c>
       <c r="B4" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153495</v>
       </c>
       <c r="B5" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137153496</v>
       </c>
       <c r="B6" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>137153497</v>
       </c>
       <c r="B7" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2026 artfynd.xlsx
+++ b/artfynd/A 43083-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153468</v>
       </c>
       <c r="B2" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153469</v>
       </c>
       <c r="B3" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153493</v>
       </c>
       <c r="B4" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153495</v>
       </c>
       <c r="B5" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137153496</v>
       </c>
       <c r="B6" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>137153497</v>
       </c>
       <c r="B7" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2026 artfynd.xlsx
+++ b/artfynd/A 43083-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153468</v>
       </c>
       <c r="B2" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153469</v>
       </c>
       <c r="B3" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153493</v>
       </c>
       <c r="B4" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153495</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137153496</v>
       </c>
       <c r="B6" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>137153497</v>
       </c>
       <c r="B7" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
